--- a/tests/workbooktests/workbooks/test_localvolatilities.xlsx
+++ b/tests/workbooktests/workbooks/test_localvolatilities.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFF1504-8737-4DB3-BD6A-66200BD27926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{220A06E8-4C10-4F72-A0E3-92BB17DAD233}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{129AA12A-F35B-4A06-8C06-708DDFE648E0}"/>
   </bookViews>
@@ -20,17 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -38,28 +27,6 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
@@ -151,7 +118,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -320,7 +287,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -653,14 +620,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6006BC1-D3B7-489F-B381-86373207D31C}">
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" customWidth="1"/>
-    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5" customWidth="1"/>
+    <col min="7" max="7" width="10.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -668,7 +635,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -685,7 +652,7 @@
       <c r="I2" s="12"/>
       <c r="J2" s="13"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -704,7 +671,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -722,19 +689,19 @@
         <v>80</v>
       </c>
       <c r="I4" s="9">
-        <f t="shared" ref="I4:J4" si="0">I3*$B$4</f>
+        <f>I3*$B$4</f>
         <v>100</v>
       </c>
       <c r="J4" s="10">
-        <f t="shared" si="0"/>
+        <f>J3*$B$4</f>
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="F5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="14" cm="1">
+      <c r="G5" s="14">
         <f t="array" ref="G5">_xll.qlCalendarAdvance($B$3,$B$1,F5)</f>
         <v>46539</v>
       </c>
@@ -748,18 +715,18 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="str" cm="1">
+      <c r="B6" t="str">
         <f t="array" ref="B6">_xll.qlBlackConstantVol(B1,B3,H5,B2)</f>
         <v>欣[test_localvolatilities.xlsx]LocalVolTermStructures!R6C2BlackVolTermStructureHandle,A</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="15" cm="1">
+      <c r="G6" s="15">
         <f t="array" ref="G6">_xll.qlCalendarAdvance($B$3,$B$1,F6)</f>
         <v>46905</v>
       </c>
@@ -773,18 +740,18 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>17</v>
       </c>
-      <c r="B7" t="str" cm="1">
-        <f t="array" ref="B7">_xll.qlFlatForward($B$1,0.03)</f>
+      <c r="B7" t="str">
+        <f>_xll.qlFlatForward($B$1,0.03,"actual365fixed")</f>
         <v>欣[test_localvolatilities.xlsx]LocalVolTermStructures!R7C2YieldTermStructureHandle,A</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="15" cm="1">
+      <c r="G7" s="15">
         <f t="array" ref="G7">_xll.qlCalendarAdvance($B$3,$B$1,F7)</f>
         <v>47270</v>
       </c>
@@ -798,18 +765,18 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" t="str" cm="1">
-        <f t="array" ref="B8">_xll.qlFlatForward($B$1,0.02)</f>
+      <c r="B8" t="str">
+        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed")</f>
         <v>欣[test_localvolatilities.xlsx]LocalVolTermStructures!R8C2YieldTermStructureHandle,A</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="15" cm="1">
+      <c r="G8" s="15">
         <f t="array" ref="G8">_xll.qlCalendarAdvance($B$3,$B$1,F8)</f>
         <v>47635</v>
       </c>
@@ -823,11 +790,11 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10">
       <c r="F9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="16" cm="1">
+      <c r="G9" s="16">
         <f t="array" ref="G9">_xll.qlCalendarAdvance($B$3,$B$1,F9)</f>
         <v>48000</v>
       </c>
@@ -841,51 +808,51 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10">
       <c r="C14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15" t="str" cm="1">
+      <c r="B15" t="str">
         <f t="array" ref="B15">_xll.qlLocalConstantVol(B1,H5,B2)</f>
         <v>欣[test_localvolatilities.xlsx]LocalVolTermStructures!R15C2LocalVolTermStructureHandle,A</v>
       </c>
-      <c r="C15" cm="1">
+      <c r="C15">
         <f t="array" ref="C15">_xll.qlLocalVolTermStructureLocalVol(B15,$G$6,$B$4)</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>19</v>
       </c>
-      <c r="B16" t="str" cm="1">
+      <c r="B16" t="str">
         <f t="array" ref="B16">_xll.qlLocalVolSurface(B6,B7,B8,B4)</f>
         <v>欣[test_localvolatilities.xlsx]LocalVolTermStructures!R16C2LocalVolTermStructureHandle,A</v>
       </c>
-      <c r="C16" cm="1">
+      <c r="C16">
         <f t="array" ref="C16">_xll.qlLocalVolTermStructureLocalVol(B16,$G$6,$B$4)</f>
         <v>0.25000000000026379</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
-      <c r="B17" t="str" cm="1">
+      <c r="B17" t="str">
         <f t="array" ref="B17">_xll.qlNoExceptLocalVolSurface(B6,B7,B8,B4,H5)</f>
         <v>欣[test_localvolatilities.xlsx]LocalVolTermStructures!R17C2LocalVolTermStructureHandle,A</v>
       </c>
-      <c r="C17" cm="1">
+      <c r="C17">
         <f t="array" ref="C17">_xll.qlLocalVolTermStructureLocalVol(B17,$G$6,$B$4)</f>
         <v>0.25000000000026379</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -893,7 +860,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -901,7 +868,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -909,15 +876,15 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>27</v>
       </c>
-      <c r="B23" t="str" cm="1">
+      <c r="B23" t="str">
         <f t="array" ref="B23">_xll.qlFixedLocalVolSurface(B1,G5:G9,H4:J4,TRANSPOSE(H5:J9),B2,B19,B20,B21)</f>
         <v>欣[test_localvolatilities.xlsx]LocalVolTermStructures!R23C2LocalVolTermStructureHandle,A</v>
       </c>
-      <c r="C23" cm="1">
+      <c r="C23">
         <f t="array" ref="C23">_xll.qlLocalVolTermStructureLocalVol(B23,$G$6,$B$4)</f>
         <v>0.25</v>
       </c>
